--- a/docs/curriculum/bscs-year1-study-plan-target-shape.xlsx
+++ b/docs/curriculum/bscs-year1-study-plan-target-shape.xlsx
@@ -552,7 +552,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BS Computer Science — 1st Year — target shape</t>
+          <t>🖥️ BS Computer Science — 1st Year — target shape</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Introduction to Computing</t>
+          <t>💻 Introduction to Computing</t>
         </is>
       </c>
       <c r="C7" s="5" t="n">
@@ -664,7 +664,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Computer Programming 1</t>
+          <t>⌨️ Computer Programming 1</t>
         </is>
       </c>
       <c r="C8" s="5" t="n">
@@ -700,7 +700,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Mathematics in the Modern World</t>
+          <t>📐 Mathematics in the Modern World</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
@@ -736,7 +736,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>The Contemporary World</t>
+          <t>🌏 The Contemporary World</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
@@ -772,7 +772,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Art Appreciation</t>
+          <t>🎨 Art Appreciation</t>
         </is>
       </c>
       <c r="C11" s="5" t="n">
@@ -808,7 +808,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Computer Programming 2</t>
+          <t>🧠 Computer Programming 2</t>
         </is>
       </c>
       <c r="C12" s="5" t="n">
@@ -844,7 +844,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Discrete Structures I</t>
+          <t>🧮 Discrete Structures I</t>
         </is>
       </c>
       <c r="C13" s="5" t="n">
@@ -880,7 +880,7 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Understanding the Self</t>
+          <t>🪞 Understanding the Self</t>
         </is>
       </c>
       <c r="C14" s="5" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Readings in Philippine History</t>
+          <t>📜 Readings in Philippine History</t>
         </is>
       </c>
       <c r="C15" s="5" t="n">
@@ -952,7 +952,7 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Purposive Communication</t>
+          <t>💬 Purposive Communication</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
@@ -1040,7 +1040,7 @@
     <row r="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>Understanding the Self</t>
+          <t>🪞 Understanding the Self</t>
         </is>
       </c>
     </row>
@@ -1460,7 +1460,7 @@
     <row r="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>Readings in Philippine History</t>
+          <t>📜 Readings in Philippine History</t>
         </is>
       </c>
     </row>
@@ -1932,7 +1932,7 @@
     <row r="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>Purposive Communication</t>
+          <t>💬 Purposive Communication</t>
         </is>
       </c>
     </row>
@@ -2519,7 +2519,7 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Computer Programming 1</t>
+          <t>⌨️ Computer Programming 1</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -2544,7 +2544,7 @@
       <c r="C6" s="6" t="inlineStr"/>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Computer Programming 1</t>
+          <t>⌨️ Computer Programming 1</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -2569,7 +2569,7 @@
       <c r="C7" s="6" t="inlineStr"/>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Computer Programming 1</t>
+          <t>⌨️ Computer Programming 1</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -2594,7 +2594,7 @@
       <c r="C8" s="6" t="inlineStr"/>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Computer Programming 1</t>
+          <t>⌨️ Computer Programming 1</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -2619,7 +2619,7 @@
       <c r="C9" s="6" t="inlineStr"/>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Computer Programming 1</t>
+          <t>⌨️ Computer Programming 1</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -2644,7 +2644,7 @@
       <c r="C10" s="6" t="inlineStr"/>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Computer Programming 1</t>
+          <t>⌨️ Computer Programming 1</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -2669,7 +2669,7 @@
       <c r="C11" s="6" t="inlineStr"/>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Computer Programming 1</t>
+          <t>⌨️ Computer Programming 1</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -2694,7 +2694,7 @@
       <c r="C12" s="6" t="inlineStr"/>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Computer Programming 1</t>
+          <t>⌨️ Computer Programming 1</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -2719,7 +2719,7 @@
       <c r="C13" s="6" t="inlineStr"/>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Computer Programming 1</t>
+          <t>⌨️ Computer Programming 1</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -2744,7 +2744,7 @@
       <c r="C14" s="6" t="inlineStr"/>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Computer Programming 1</t>
+          <t>⌨️ Computer Programming 1</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -2769,7 +2769,7 @@
       <c r="C15" s="6" t="inlineStr"/>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Computer Programming 1</t>
+          <t>⌨️ Computer Programming 1</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -2794,7 +2794,7 @@
       <c r="C16" s="6" t="inlineStr"/>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Computer Programming 1</t>
+          <t>⌨️ Computer Programming 1</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -2819,7 +2819,7 @@
       <c r="C17" s="6" t="inlineStr"/>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>Computer Programming 1</t>
+          <t>⌨️ Computer Programming 1</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -2844,7 +2844,7 @@
       <c r="C18" s="6" t="inlineStr"/>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Computer Programming 1</t>
+          <t>⌨️ Computer Programming 1</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -2869,7 +2869,7 @@
       <c r="C19" s="6" t="inlineStr"/>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>Computer Programming 1</t>
+          <t>⌨️ Computer Programming 1</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -2894,7 +2894,7 @@
       <c r="C20" s="6" t="inlineStr"/>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Computer Programming 1</t>
+          <t>⌨️ Computer Programming 1</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -2919,7 +2919,7 @@
       <c r="C21" s="6" t="inlineStr"/>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>Computer Programming 1</t>
+          <t>⌨️ Computer Programming 1</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -2944,7 +2944,7 @@
       <c r="C22" s="6" t="inlineStr"/>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Computer Programming 1</t>
+          <t>⌨️ Computer Programming 1</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -2969,7 +2969,7 @@
       <c r="C23" s="6" t="inlineStr"/>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>Computer Programming 1</t>
+          <t>⌨️ Computer Programming 1</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -2994,7 +2994,7 @@
       <c r="C24" s="6" t="inlineStr"/>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Computer Programming 1</t>
+          <t>⌨️ Computer Programming 1</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -3019,7 +3019,7 @@
       <c r="C25" s="6" t="inlineStr"/>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Computer Programming 1</t>
+          <t>⌨️ Computer Programming 1</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -3044,7 +3044,7 @@
       <c r="C26" s="6" t="inlineStr"/>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Computer Programming 1</t>
+          <t>⌨️ Computer Programming 1</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -3069,7 +3069,7 @@
       <c r="C27" s="6" t="inlineStr"/>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Computer Programming 1</t>
+          <t>⌨️ Computer Programming 1</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -3094,7 +3094,7 @@
       <c r="C28" s="6" t="inlineStr"/>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Computer Programming 1</t>
+          <t>⌨️ Computer Programming 1</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -3119,7 +3119,7 @@
       <c r="C29" s="6" t="inlineStr"/>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Computer Programming 1</t>
+          <t>⌨️ Computer Programming 1</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -3144,7 +3144,7 @@
       <c r="C30" s="6" t="inlineStr"/>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Computer Programming 1</t>
+          <t>⌨️ Computer Programming 1</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -3169,7 +3169,7 @@
       <c r="C31" s="6" t="inlineStr"/>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Computer Programming 1</t>
+          <t>⌨️ Computer Programming 1</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -3194,7 +3194,7 @@
       <c r="C32" s="6" t="inlineStr"/>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Computer Programming 1</t>
+          <t>⌨️ Computer Programming 1</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -3219,7 +3219,7 @@
       <c r="C33" s="6" t="inlineStr"/>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Computer Programming 1</t>
+          <t>⌨️ Computer Programming 1</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -3244,7 +3244,7 @@
       <c r="C34" s="6" t="inlineStr"/>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Computer Programming 1</t>
+          <t>⌨️ Computer Programming 1</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -3269,7 +3269,7 @@
       <c r="C35" s="6" t="inlineStr"/>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Computer Programming 1</t>
+          <t>⌨️ Computer Programming 1</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -3294,7 +3294,7 @@
       <c r="C36" s="6" t="inlineStr"/>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>Computer Programming 1</t>
+          <t>⌨️ Computer Programming 1</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -3319,7 +3319,7 @@
       <c r="C37" s="6" t="inlineStr"/>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Computer Programming 1</t>
+          <t>⌨️ Computer Programming 1</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -3344,7 +3344,7 @@
       <c r="C38" s="6" t="inlineStr"/>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Computer Programming 1</t>
+          <t>⌨️ Computer Programming 1</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -3369,7 +3369,7 @@
       <c r="C39" s="6" t="inlineStr"/>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Computer Programming 1</t>
+          <t>⌨️ Computer Programming 1</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -3394,7 +3394,7 @@
       <c r="C40" s="6" t="inlineStr"/>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Computer Programming 1</t>
+          <t>⌨️ Computer Programming 1</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -3419,7 +3419,7 @@
       <c r="C41" s="6" t="inlineStr"/>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>Computer Programming 1</t>
+          <t>⌨️ Computer Programming 1</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -3444,7 +3444,7 @@
       <c r="C42" s="6" t="inlineStr"/>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>Computer Programming 1</t>
+          <t>⌨️ Computer Programming 1</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -3469,7 +3469,7 @@
       <c r="C43" s="6" t="inlineStr"/>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>Computer Programming 1</t>
+          <t>⌨️ Computer Programming 1</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -3494,7 +3494,7 @@
       <c r="C44" s="6" t="inlineStr"/>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>Computer Programming 1</t>
+          <t>⌨️ Computer Programming 1</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -3519,7 +3519,7 @@
       <c r="C45" s="6" t="inlineStr"/>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Computer Programming 2</t>
+          <t>🧠 Computer Programming 2</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -3544,7 +3544,7 @@
       <c r="C46" s="6" t="inlineStr"/>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Computer Programming 2</t>
+          <t>🧠 Computer Programming 2</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -3569,7 +3569,7 @@
       <c r="C47" s="6" t="inlineStr"/>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>Computer Programming 2</t>
+          <t>🧠 Computer Programming 2</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -3594,7 +3594,7 @@
       <c r="C48" s="6" t="inlineStr"/>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>Computer Programming 2</t>
+          <t>🧠 Computer Programming 2</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -3619,7 +3619,7 @@
       <c r="C49" s="6" t="inlineStr"/>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>Computer Programming 2</t>
+          <t>🧠 Computer Programming 2</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -3644,7 +3644,7 @@
       <c r="C50" s="6" t="inlineStr"/>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>Computer Programming 2</t>
+          <t>🧠 Computer Programming 2</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -3669,7 +3669,7 @@
       <c r="C51" s="6" t="inlineStr"/>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>Computer Programming 2</t>
+          <t>🧠 Computer Programming 2</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -3694,7 +3694,7 @@
       <c r="C52" s="6" t="inlineStr"/>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>Computer Programming 2</t>
+          <t>🧠 Computer Programming 2</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -3719,7 +3719,7 @@
       <c r="C53" s="6" t="inlineStr"/>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>Computer Programming 2</t>
+          <t>🧠 Computer Programming 2</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -3744,7 +3744,7 @@
       <c r="C54" s="6" t="inlineStr"/>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Computer Programming 2</t>
+          <t>🧠 Computer Programming 2</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -3769,7 +3769,7 @@
       <c r="C55" s="6" t="inlineStr"/>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>Computer Programming 2</t>
+          <t>🧠 Computer Programming 2</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -3794,7 +3794,7 @@
       <c r="C56" s="6" t="inlineStr"/>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>Computer Programming 2</t>
+          <t>🧠 Computer Programming 2</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -3819,7 +3819,7 @@
       <c r="C57" s="6" t="inlineStr"/>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>Computer Programming 2</t>
+          <t>🧠 Computer Programming 2</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -3844,7 +3844,7 @@
       <c r="C58" s="6" t="inlineStr"/>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>Computer Programming 2</t>
+          <t>🧠 Computer Programming 2</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -3869,7 +3869,7 @@
       <c r="C59" s="6" t="inlineStr"/>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>Computer Programming 2</t>
+          <t>🧠 Computer Programming 2</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -3894,7 +3894,7 @@
       <c r="C60" s="6" t="inlineStr"/>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>Computer Programming 2</t>
+          <t>🧠 Computer Programming 2</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -3919,7 +3919,7 @@
       <c r="C61" s="6" t="inlineStr"/>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>Computer Programming 2</t>
+          <t>🧠 Computer Programming 2</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -3944,7 +3944,7 @@
       <c r="C62" s="6" t="inlineStr"/>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>Computer Programming 2</t>
+          <t>🧠 Computer Programming 2</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -3969,7 +3969,7 @@
       <c r="C63" s="6" t="inlineStr"/>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>Computer Programming 2</t>
+          <t>🧠 Computer Programming 2</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -3994,7 +3994,7 @@
       <c r="C64" s="6" t="inlineStr"/>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>Computer Programming 2</t>
+          <t>🧠 Computer Programming 2</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -4019,7 +4019,7 @@
       <c r="C65" s="6" t="inlineStr"/>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>Computer Programming 2</t>
+          <t>🧠 Computer Programming 2</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -4044,7 +4044,7 @@
       <c r="C66" s="6" t="inlineStr"/>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>Computer Programming 2</t>
+          <t>🧠 Computer Programming 2</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -4069,7 +4069,7 @@
       <c r="C67" s="6" t="inlineStr"/>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>Computer Programming 2</t>
+          <t>🧠 Computer Programming 2</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -4094,7 +4094,7 @@
       <c r="C68" s="6" t="inlineStr"/>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>Computer Programming 2</t>
+          <t>🧠 Computer Programming 2</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -4129,7 +4129,7 @@
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>Discrete Structures I</t>
+          <t>🧮 Discrete Structures I</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -4154,7 +4154,7 @@
       <c r="C71" s="6" t="inlineStr"/>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>Discrete Structures I</t>
+          <t>🧮 Discrete Structures I</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
@@ -4179,7 +4179,7 @@
       <c r="C72" s="6" t="inlineStr"/>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>Discrete Structures I</t>
+          <t>🧮 Discrete Structures I</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
@@ -4204,7 +4204,7 @@
       <c r="C73" s="6" t="inlineStr"/>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>Discrete Structures I</t>
+          <t>🧮 Discrete Structures I</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
@@ -4229,7 +4229,7 @@
       <c r="C74" s="6" t="inlineStr"/>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>Discrete Structures I</t>
+          <t>🧮 Discrete Structures I</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
@@ -4254,7 +4254,7 @@
       <c r="C75" s="6" t="inlineStr"/>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>Discrete Structures I</t>
+          <t>🧮 Discrete Structures I</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
@@ -4279,7 +4279,7 @@
       <c r="C76" s="6" t="inlineStr"/>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>Discrete Structures I</t>
+          <t>🧮 Discrete Structures I</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
@@ -4304,7 +4304,7 @@
       <c r="C77" s="6" t="inlineStr"/>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>Discrete Structures I</t>
+          <t>🧮 Discrete Structures I</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
@@ -4329,7 +4329,7 @@
       <c r="C78" s="6" t="inlineStr"/>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>Discrete Structures I</t>
+          <t>🧮 Discrete Structures I</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
@@ -4354,7 +4354,7 @@
       <c r="C79" s="6" t="inlineStr"/>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>Discrete Structures I</t>
+          <t>🧮 Discrete Structures I</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
@@ -4379,7 +4379,7 @@
       <c r="C80" s="6" t="inlineStr"/>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>Discrete Structures I</t>
+          <t>🧮 Discrete Structures I</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
@@ -4404,7 +4404,7 @@
       <c r="C81" s="6" t="inlineStr"/>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>Discrete Structures I</t>
+          <t>🧮 Discrete Structures I</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
@@ -4429,7 +4429,7 @@
       <c r="C82" s="6" t="inlineStr"/>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>Discrete Structures I</t>
+          <t>🧮 Discrete Structures I</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
@@ -4454,7 +4454,7 @@
       <c r="C83" s="6" t="inlineStr"/>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>Discrete Structures I</t>
+          <t>🧮 Discrete Structures I</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
@@ -4479,7 +4479,7 @@
       <c r="C84" s="6" t="inlineStr"/>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>Discrete Structures I</t>
+          <t>🧮 Discrete Structures I</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
@@ -4504,7 +4504,7 @@
       <c r="C85" s="6" t="inlineStr"/>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>Discrete Structures I</t>
+          <t>🧮 Discrete Structures I</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
@@ -4529,7 +4529,7 @@
       <c r="C86" s="6" t="inlineStr"/>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>Discrete Structures I</t>
+          <t>🧮 Discrete Structures I</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
@@ -4554,7 +4554,7 @@
       <c r="C87" s="6" t="inlineStr"/>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>Discrete Structures I</t>
+          <t>🧮 Discrete Structures I</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
@@ -4579,7 +4579,7 @@
       <c r="C88" s="6" t="inlineStr"/>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>Discrete Structures I</t>
+          <t>🧮 Discrete Structures I</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
@@ -4604,7 +4604,7 @@
       <c r="C89" s="6" t="inlineStr"/>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>Discrete Structures I</t>
+          <t>🧮 Discrete Structures I</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
@@ -4629,7 +4629,7 @@
       <c r="C90" s="6" t="inlineStr"/>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>Discrete Structures I</t>
+          <t>🧮 Discrete Structures I</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
@@ -4654,7 +4654,7 @@
       <c r="C91" s="6" t="inlineStr"/>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>Discrete Structures I</t>
+          <t>🧮 Discrete Structures I</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
@@ -4679,7 +4679,7 @@
       <c r="C92" s="6" t="inlineStr"/>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>Discrete Structures I</t>
+          <t>🧮 Discrete Structures I</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
@@ -4704,7 +4704,7 @@
       <c r="C93" s="6" t="inlineStr"/>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>Discrete Structures I</t>
+          <t>🧮 Discrete Structures I</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
@@ -4729,7 +4729,7 @@
       <c r="C94" s="6" t="inlineStr"/>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>Discrete Structures I</t>
+          <t>🧮 Discrete Structures I</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
@@ -4754,7 +4754,7 @@
       <c r="C95" s="6" t="inlineStr"/>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>Discrete Structures I</t>
+          <t>🧮 Discrete Structures I</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
@@ -4779,7 +4779,7 @@
       <c r="C96" s="6" t="inlineStr"/>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>Discrete Structures I</t>
+          <t>🧮 Discrete Structures I</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
@@ -4804,7 +4804,7 @@
       <c r="C97" s="6" t="inlineStr"/>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>Discrete Structures I</t>
+          <t>🧮 Discrete Structures I</t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr">
@@ -4829,7 +4829,7 @@
       <c r="C98" s="6" t="inlineStr"/>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>Discrete Structures I</t>
+          <t>🧮 Discrete Structures I</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
@@ -4854,7 +4854,7 @@
       <c r="C99" s="6" t="inlineStr"/>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>Discrete Structures I</t>
+          <t>🧮 Discrete Structures I</t>
         </is>
       </c>
       <c r="E99" s="5" t="inlineStr">
@@ -4879,7 +4879,7 @@
       <c r="C100" s="6" t="inlineStr"/>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>Discrete Structures I</t>
+          <t>🧮 Discrete Structures I</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
@@ -4904,7 +4904,7 @@
       <c r="C101" s="6" t="inlineStr"/>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>Discrete Structures I</t>
+          <t>🧮 Discrete Structures I</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr">
@@ -4929,7 +4929,7 @@
       <c r="C102" s="6" t="inlineStr"/>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>Discrete Structures I</t>
+          <t>🧮 Discrete Structures I</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>Introduction to Computing</t>
+          <t>💻 Introduction to Computing</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
@@ -4989,7 +4989,7 @@
       <c r="C105" s="6" t="inlineStr"/>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>Introduction to Computing</t>
+          <t>💻 Introduction to Computing</t>
         </is>
       </c>
       <c r="E105" s="5" t="inlineStr">
@@ -5014,7 +5014,7 @@
       <c r="C106" s="6" t="inlineStr"/>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>Introduction to Computing</t>
+          <t>💻 Introduction to Computing</t>
         </is>
       </c>
       <c r="E106" s="5" t="inlineStr">
@@ -5039,7 +5039,7 @@
       <c r="C107" s="6" t="inlineStr"/>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>Introduction to Computing</t>
+          <t>💻 Introduction to Computing</t>
         </is>
       </c>
       <c r="E107" s="5" t="inlineStr">
@@ -5064,7 +5064,7 @@
       <c r="C108" s="6" t="inlineStr"/>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>Introduction to Computing</t>
+          <t>💻 Introduction to Computing</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
@@ -5089,7 +5089,7 @@
       <c r="C109" s="6" t="inlineStr"/>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>Introduction to Computing</t>
+          <t>💻 Introduction to Computing</t>
         </is>
       </c>
       <c r="E109" s="5" t="inlineStr">
@@ -5114,7 +5114,7 @@
       <c r="C110" s="6" t="inlineStr"/>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>Introduction to Computing</t>
+          <t>💻 Introduction to Computing</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
@@ -5139,7 +5139,7 @@
       <c r="C111" s="6" t="inlineStr"/>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>Introduction to Computing</t>
+          <t>💻 Introduction to Computing</t>
         </is>
       </c>
       <c r="E111" s="5" t="inlineStr">
@@ -5164,7 +5164,7 @@
       <c r="C112" s="6" t="inlineStr"/>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>Introduction to Computing</t>
+          <t>💻 Introduction to Computing</t>
         </is>
       </c>
       <c r="E112" s="5" t="inlineStr">
@@ -5189,7 +5189,7 @@
       <c r="C113" s="6" t="inlineStr"/>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>Introduction to Computing</t>
+          <t>💻 Introduction to Computing</t>
         </is>
       </c>
       <c r="E113" s="5" t="inlineStr">
@@ -5214,7 +5214,7 @@
       <c r="C114" s="6" t="inlineStr"/>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>Introduction to Computing</t>
+          <t>💻 Introduction to Computing</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr">
@@ -5239,7 +5239,7 @@
       <c r="C115" s="6" t="inlineStr"/>
       <c r="D115" s="5" t="inlineStr">
         <is>
-          <t>Introduction to Computing</t>
+          <t>💻 Introduction to Computing</t>
         </is>
       </c>
       <c r="E115" s="5" t="inlineStr">
@@ -5264,7 +5264,7 @@
       <c r="C116" s="6" t="inlineStr"/>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>Introduction to Computing</t>
+          <t>💻 Introduction to Computing</t>
         </is>
       </c>
       <c r="E116" s="5" t="inlineStr">
@@ -5289,7 +5289,7 @@
       <c r="C117" s="6" t="inlineStr"/>
       <c r="D117" s="5" t="inlineStr">
         <is>
-          <t>Introduction to Computing</t>
+          <t>💻 Introduction to Computing</t>
         </is>
       </c>
       <c r="E117" s="5" t="inlineStr">
@@ -5314,7 +5314,7 @@
       <c r="C118" s="6" t="inlineStr"/>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>Introduction to Computing</t>
+          <t>💻 Introduction to Computing</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr">
@@ -5339,7 +5339,7 @@
       <c r="C119" s="6" t="inlineStr"/>
       <c r="D119" s="5" t="inlineStr">
         <is>
-          <t>Introduction to Computing</t>
+          <t>💻 Introduction to Computing</t>
         </is>
       </c>
       <c r="E119" s="5" t="inlineStr">
@@ -5364,7 +5364,7 @@
       <c r="C120" s="6" t="inlineStr"/>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>Introduction to Computing</t>
+          <t>💻 Introduction to Computing</t>
         </is>
       </c>
       <c r="E120" s="5" t="inlineStr">
@@ -5389,7 +5389,7 @@
       <c r="C121" s="6" t="inlineStr"/>
       <c r="D121" s="5" t="inlineStr">
         <is>
-          <t>Introduction to Computing</t>
+          <t>💻 Introduction to Computing</t>
         </is>
       </c>
       <c r="E121" s="5" t="inlineStr">
@@ -5414,7 +5414,7 @@
       <c r="C122" s="6" t="inlineStr"/>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>Introduction to Computing</t>
+          <t>💻 Introduction to Computing</t>
         </is>
       </c>
       <c r="E122" s="5" t="inlineStr">
@@ -5439,7 +5439,7 @@
       <c r="C123" s="6" t="inlineStr"/>
       <c r="D123" s="5" t="inlineStr">
         <is>
-          <t>Introduction to Computing</t>
+          <t>💻 Introduction to Computing</t>
         </is>
       </c>
       <c r="E123" s="5" t="inlineStr">
@@ -5464,7 +5464,7 @@
       <c r="C124" s="6" t="inlineStr"/>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>Introduction to Computing</t>
+          <t>💻 Introduction to Computing</t>
         </is>
       </c>
       <c r="E124" s="5" t="inlineStr">
@@ -5489,7 +5489,7 @@
       <c r="C125" s="6" t="inlineStr"/>
       <c r="D125" s="5" t="inlineStr">
         <is>
-          <t>Introduction to Computing</t>
+          <t>💻 Introduction to Computing</t>
         </is>
       </c>
       <c r="E125" s="5" t="inlineStr">
@@ -5514,7 +5514,7 @@
       <c r="C126" s="6" t="inlineStr"/>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>Introduction to Computing</t>
+          <t>💻 Introduction to Computing</t>
         </is>
       </c>
       <c r="E126" s="5" t="inlineStr">
@@ -5539,7 +5539,7 @@
       <c r="C127" s="6" t="inlineStr"/>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>Introduction to Computing</t>
+          <t>💻 Introduction to Computing</t>
         </is>
       </c>
       <c r="E127" s="5" t="inlineStr">
@@ -5564,7 +5564,7 @@
       <c r="C128" s="6" t="inlineStr"/>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>Introduction to Computing</t>
+          <t>💻 Introduction to Computing</t>
         </is>
       </c>
       <c r="E128" s="5" t="inlineStr">
@@ -5599,7 +5599,7 @@
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>Mathematics in the Modern World</t>
+          <t>📐 Mathematics in the Modern World</t>
         </is>
       </c>
       <c r="E130" s="5" t="inlineStr">
@@ -5624,7 +5624,7 @@
       <c r="C131" s="6" t="inlineStr"/>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t>Mathematics in the Modern World</t>
+          <t>📐 Mathematics in the Modern World</t>
         </is>
       </c>
       <c r="E131" s="5" t="inlineStr">
@@ -5649,7 +5649,7 @@
       <c r="C132" s="6" t="inlineStr"/>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>Mathematics in the Modern World</t>
+          <t>📐 Mathematics in the Modern World</t>
         </is>
       </c>
       <c r="E132" s="5" t="inlineStr">
@@ -5674,7 +5674,7 @@
       <c r="C133" s="6" t="inlineStr"/>
       <c r="D133" s="5" t="inlineStr">
         <is>
-          <t>Mathematics in the Modern World</t>
+          <t>📐 Mathematics in the Modern World</t>
         </is>
       </c>
       <c r="E133" s="5" t="inlineStr">
@@ -5699,7 +5699,7 @@
       <c r="C134" s="6" t="inlineStr"/>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>Mathematics in the Modern World</t>
+          <t>📐 Mathematics in the Modern World</t>
         </is>
       </c>
       <c r="E134" s="5" t="inlineStr">
@@ -5724,7 +5724,7 @@
       <c r="C135" s="6" t="inlineStr"/>
       <c r="D135" s="5" t="inlineStr">
         <is>
-          <t>Mathematics in the Modern World</t>
+          <t>📐 Mathematics in the Modern World</t>
         </is>
       </c>
       <c r="E135" s="5" t="inlineStr">
@@ -5749,7 +5749,7 @@
       <c r="C136" s="6" t="inlineStr"/>
       <c r="D136" s="5" t="inlineStr">
         <is>
-          <t>Mathematics in the Modern World</t>
+          <t>📐 Mathematics in the Modern World</t>
         </is>
       </c>
       <c r="E136" s="5" t="inlineStr">
@@ -5774,7 +5774,7 @@
       <c r="C137" s="6" t="inlineStr"/>
       <c r="D137" s="5" t="inlineStr">
         <is>
-          <t>Mathematics in the Modern World</t>
+          <t>📐 Mathematics in the Modern World</t>
         </is>
       </c>
       <c r="E137" s="5" t="inlineStr">
@@ -5799,7 +5799,7 @@
       <c r="C138" s="6" t="inlineStr"/>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>Mathematics in the Modern World</t>
+          <t>📐 Mathematics in the Modern World</t>
         </is>
       </c>
       <c r="E138" s="5" t="inlineStr">
@@ -5824,7 +5824,7 @@
       <c r="C139" s="6" t="inlineStr"/>
       <c r="D139" s="5" t="inlineStr">
         <is>
-          <t>Mathematics in the Modern World</t>
+          <t>📐 Mathematics in the Modern World</t>
         </is>
       </c>
       <c r="E139" s="5" t="inlineStr">
@@ -5849,7 +5849,7 @@
       <c r="C140" s="6" t="inlineStr"/>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>Mathematics in the Modern World</t>
+          <t>📐 Mathematics in the Modern World</t>
         </is>
       </c>
       <c r="E140" s="5" t="inlineStr">
@@ -5874,7 +5874,7 @@
       <c r="C141" s="6" t="inlineStr"/>
       <c r="D141" s="5" t="inlineStr">
         <is>
-          <t>Mathematics in the Modern World</t>
+          <t>📐 Mathematics in the Modern World</t>
         </is>
       </c>
       <c r="E141" s="5" t="inlineStr">
@@ -5899,7 +5899,7 @@
       <c r="C142" s="6" t="inlineStr"/>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>Mathematics in the Modern World</t>
+          <t>📐 Mathematics in the Modern World</t>
         </is>
       </c>
       <c r="E142" s="5" t="inlineStr">
@@ -5924,7 +5924,7 @@
       <c r="C143" s="6" t="inlineStr"/>
       <c r="D143" s="5" t="inlineStr">
         <is>
-          <t>Mathematics in the Modern World</t>
+          <t>📐 Mathematics in the Modern World</t>
         </is>
       </c>
       <c r="E143" s="5" t="inlineStr">
@@ -5949,7 +5949,7 @@
       <c r="C144" s="6" t="inlineStr"/>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>Mathematics in the Modern World</t>
+          <t>📐 Mathematics in the Modern World</t>
         </is>
       </c>
       <c r="E144" s="5" t="inlineStr">
@@ -5974,7 +5974,7 @@
       <c r="C145" s="6" t="inlineStr"/>
       <c r="D145" s="5" t="inlineStr">
         <is>
-          <t>Mathematics in the Modern World</t>
+          <t>📐 Mathematics in the Modern World</t>
         </is>
       </c>
       <c r="E145" s="5" t="inlineStr">
@@ -6009,7 +6009,7 @@
       </c>
       <c r="D147" s="5" t="inlineStr">
         <is>
-          <t>Computer Programming 2</t>
+          <t>🧠 Computer Programming 2</t>
         </is>
       </c>
       <c r="E147" s="5" t="inlineStr">
@@ -6034,7 +6034,7 @@
       <c r="C148" s="6" t="inlineStr"/>
       <c r="D148" s="5" t="inlineStr">
         <is>
-          <t>Computer Programming 2</t>
+          <t>🧠 Computer Programming 2</t>
         </is>
       </c>
       <c r="E148" s="5" t="inlineStr">
@@ -6059,7 +6059,7 @@
       <c r="C149" s="6" t="inlineStr"/>
       <c r="D149" s="5" t="inlineStr">
         <is>
-          <t>Computer Programming 2</t>
+          <t>🧠 Computer Programming 2</t>
         </is>
       </c>
       <c r="E149" s="5" t="inlineStr">
@@ -6084,7 +6084,7 @@
       <c r="C150" s="6" t="inlineStr"/>
       <c r="D150" s="5" t="inlineStr">
         <is>
-          <t>Computer Programming 2</t>
+          <t>🧠 Computer Programming 2</t>
         </is>
       </c>
       <c r="E150" s="5" t="inlineStr">
@@ -6109,7 +6109,7 @@
       <c r="C151" s="6" t="inlineStr"/>
       <c r="D151" s="5" t="inlineStr">
         <is>
-          <t>Computer Programming 2</t>
+          <t>🧠 Computer Programming 2</t>
         </is>
       </c>
       <c r="E151" s="5" t="inlineStr">
@@ -6134,7 +6134,7 @@
       <c r="C152" s="6" t="inlineStr"/>
       <c r="D152" s="5" t="inlineStr">
         <is>
-          <t>Computer Programming 2</t>
+          <t>🧠 Computer Programming 2</t>
         </is>
       </c>
       <c r="E152" s="5" t="inlineStr">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="D154" s="5" t="inlineStr">
         <is>
-          <t>Introduction to Computing</t>
+          <t>💻 Introduction to Computing</t>
         </is>
       </c>
       <c r="E154" s="5" t="inlineStr">
@@ -6194,7 +6194,7 @@
       <c r="C155" s="6" t="inlineStr"/>
       <c r="D155" s="5" t="inlineStr">
         <is>
-          <t>Introduction to Computing</t>
+          <t>💻 Introduction to Computing</t>
         </is>
       </c>
       <c r="E155" s="5" t="inlineStr">
@@ -6219,7 +6219,7 @@
       <c r="C156" s="6" t="inlineStr"/>
       <c r="D156" s="5" t="inlineStr">
         <is>
-          <t>Introduction to Computing</t>
+          <t>💻 Introduction to Computing</t>
         </is>
       </c>
       <c r="E156" s="5" t="inlineStr">
@@ -6244,7 +6244,7 @@
       <c r="C157" s="6" t="inlineStr"/>
       <c r="D157" s="5" t="inlineStr">
         <is>
-          <t>Introduction to Computing</t>
+          <t>💻 Introduction to Computing</t>
         </is>
       </c>
       <c r="E157" s="5" t="inlineStr">
@@ -6269,7 +6269,7 @@
       <c r="C158" s="6" t="inlineStr"/>
       <c r="D158" s="5" t="inlineStr">
         <is>
-          <t>Introduction to Computing</t>
+          <t>💻 Introduction to Computing</t>
         </is>
       </c>
       <c r="E158" s="5" t="inlineStr">
@@ -6304,7 +6304,7 @@
       </c>
       <c r="D160" s="5" t="inlineStr">
         <is>
-          <t>Purposive Communication</t>
+          <t>💬 Purposive Communication</t>
         </is>
       </c>
       <c r="E160" s="5" t="inlineStr">
@@ -6329,7 +6329,7 @@
       <c r="C161" s="6" t="inlineStr"/>
       <c r="D161" s="5" t="inlineStr">
         <is>
-          <t>Purposive Communication</t>
+          <t>💬 Purposive Communication</t>
         </is>
       </c>
       <c r="E161" s="5" t="inlineStr">
@@ -6354,7 +6354,7 @@
       <c r="C162" s="6" t="inlineStr"/>
       <c r="D162" s="5" t="inlineStr">
         <is>
-          <t>Purposive Communication</t>
+          <t>💬 Purposive Communication</t>
         </is>
       </c>
       <c r="E162" s="5" t="inlineStr">
@@ -6379,7 +6379,7 @@
       <c r="C163" s="6" t="inlineStr"/>
       <c r="D163" s="5" t="inlineStr">
         <is>
-          <t>Purposive Communication</t>
+          <t>💬 Purposive Communication</t>
         </is>
       </c>
       <c r="E163" s="5" t="inlineStr">
@@ -6414,7 +6414,7 @@
       </c>
       <c r="D165" s="5" t="inlineStr">
         <is>
-          <t>Introduction to Computing</t>
+          <t>💻 Introduction to Computing</t>
         </is>
       </c>
       <c r="E165" s="5" t="inlineStr">
@@ -6439,7 +6439,7 @@
       <c r="C166" s="6" t="inlineStr"/>
       <c r="D166" s="5" t="inlineStr">
         <is>
-          <t>Introduction to Computing</t>
+          <t>💻 Introduction to Computing</t>
         </is>
       </c>
       <c r="E166" s="5" t="inlineStr">
@@ -6464,7 +6464,7 @@
       <c r="C167" s="6" t="inlineStr"/>
       <c r="D167" s="5" t="inlineStr">
         <is>
-          <t>Introduction to Computing</t>
+          <t>💻 Introduction to Computing</t>
         </is>
       </c>
       <c r="E167" s="5" t="inlineStr">
@@ -6489,7 +6489,7 @@
       <c r="C168" s="6" t="inlineStr"/>
       <c r="D168" s="5" t="inlineStr">
         <is>
-          <t>Introduction to Computing</t>
+          <t>💻 Introduction to Computing</t>
         </is>
       </c>
       <c r="E168" s="5" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="D170" s="5" t="inlineStr">
         <is>
-          <t>Introduction to Computing</t>
+          <t>💻 Introduction to Computing</t>
         </is>
       </c>
       <c r="E170" s="5" t="inlineStr">
@@ -6549,7 +6549,7 @@
       <c r="C171" s="6" t="inlineStr"/>
       <c r="D171" s="5" t="inlineStr">
         <is>
-          <t>Introduction to Computing</t>
+          <t>💻 Introduction to Computing</t>
         </is>
       </c>
       <c r="E171" s="5" t="inlineStr">
@@ -6574,7 +6574,7 @@
       <c r="C172" s="6" t="inlineStr"/>
       <c r="D172" s="5" t="inlineStr">
         <is>
-          <t>Introduction to Computing</t>
+          <t>💻 Introduction to Computing</t>
         </is>
       </c>
       <c r="E172" s="5" t="inlineStr">
@@ -6609,7 +6609,7 @@
       </c>
       <c r="D174" s="5" t="inlineStr">
         <is>
-          <t>Understanding the Self</t>
+          <t>🪞 Understanding the Self</t>
         </is>
       </c>
       <c r="E174" s="5" t="inlineStr">
@@ -6634,7 +6634,7 @@
       <c r="C175" s="6" t="inlineStr"/>
       <c r="D175" s="5" t="inlineStr">
         <is>
-          <t>Understanding the Self</t>
+          <t>🪞 Understanding the Self</t>
         </is>
       </c>
       <c r="E175" s="5" t="inlineStr">
@@ -6669,7 +6669,7 @@
       </c>
       <c r="D177" s="5" t="inlineStr">
         <is>
-          <t>The Contemporary World</t>
+          <t>🌏 The Contemporary World</t>
         </is>
       </c>
       <c r="E177" s="5" t="inlineStr">
@@ -7074,7 +7074,7 @@
     <row r="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>Introduction to Computing</t>
+          <t>💻 Introduction to Computing</t>
         </is>
       </c>
     </row>
@@ -8450,7 +8450,7 @@
     <row r="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>Computer Programming 1</t>
+          <t>⌨️ Computer Programming 1</t>
         </is>
       </c>
     </row>
@@ -9934,7 +9934,7 @@
     <row r="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>Mathematics in the Modern World</t>
+          <t>📐 Mathematics in the Modern World</t>
         </is>
       </c>
     </row>
@@ -10886,7 +10886,7 @@
     <row r="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>The Contemporary World</t>
+          <t>🌏 The Contemporary World</t>
         </is>
       </c>
     </row>
@@ -11314,7 +11314,7 @@
     <row r="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>Art Appreciation</t>
+          <t>🎨 Art Appreciation</t>
         </is>
       </c>
     </row>
@@ -11674,7 +11674,7 @@
     <row r="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>Computer Programming 2</t>
+          <t>🧠 Computer Programming 2</t>
         </is>
       </c>
     </row>
@@ -12806,7 +12806,7 @@
     <row r="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>Discrete Structures I</t>
+          <t>🧮 Discrete Structures I</t>
         </is>
       </c>
     </row>
